--- a/output_data/charts/0500000US39049.xlsx
+++ b/output_data/charts/0500000US39049.xlsx
@@ -161,10 +161,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$13</c:f>
+              <c:f>Sheet1!$A$2:$A$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>2012</c:v>
                 </c:pt>
@@ -200,51 +200,57 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$13</c:f>
+              <c:f>Sheet1!$B$2:$B$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>2.419039460697592</c:v>
+                  <c:v>2.495390975623382</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.494498788808965</c:v>
+                  <c:v>2.588805266369571</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.572244593851449</c:v>
+                  <c:v>2.60772382962871</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.594858399780038</c:v>
+                  <c:v>2.624931262029145</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.686834510896607</c:v>
+                  <c:v>2.711712608219723</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.742927043472806</c:v>
+                  <c:v>2.744495326516529</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.927309061387623</c:v>
+                  <c:v>2.950727533878724</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.975880488639576</c:v>
+                  <c:v>3.005639293525972</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.221236137681055</c:v>
+                  <c:v>3.357565764820505</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.535683959966035</c:v>
+                  <c:v>3.549603975556453</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.708249204903862</c:v>
+                  <c:v>3.734642437678979</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>3.876469828143171</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.798017796426246</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -664,7 +670,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" style="1" customWidth="1"/>
@@ -683,7 +689,7 @@
         <v>2012</v>
       </c>
       <c r="B2" s="1">
-        <v>2.419039460697592</v>
+        <v>2.495390975623382</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -691,7 +697,7 @@
         <v>2013</v>
       </c>
       <c r="B3" s="1">
-        <v>2.494498788808965</v>
+        <v>2.588805266369571</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -699,7 +705,7 @@
         <v>2014</v>
       </c>
       <c r="B4" s="1">
-        <v>2.572244593851449</v>
+        <v>2.60772382962871</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -707,7 +713,7 @@
         <v>2015</v>
       </c>
       <c r="B5" s="1">
-        <v>2.594858399780038</v>
+        <v>2.624931262029145</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -715,7 +721,7 @@
         <v>2016</v>
       </c>
       <c r="B6" s="1">
-        <v>2.686834510896607</v>
+        <v>2.711712608219723</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -723,7 +729,7 @@
         <v>2017</v>
       </c>
       <c r="B7" s="1">
-        <v>2.742927043472806</v>
+        <v>2.744495326516529</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -731,7 +737,7 @@
         <v>2018</v>
       </c>
       <c r="B8" s="1">
-        <v>2.927309061387623</v>
+        <v>2.950727533878724</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -739,7 +745,7 @@
         <v>2019</v>
       </c>
       <c r="B9" s="1">
-        <v>2.975880488639576</v>
+        <v>3.005639293525972</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -747,7 +753,7 @@
         <v>2020</v>
       </c>
       <c r="B10" s="1">
-        <v>3.221236137681055</v>
+        <v>3.357565764820505</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -755,7 +761,7 @@
         <v>2021</v>
       </c>
       <c r="B11" s="1">
-        <v>3.535683959966035</v>
+        <v>3.549603975556453</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -763,7 +769,7 @@
         <v>2022</v>
       </c>
       <c r="B12" s="1">
-        <v>3.708249204903862</v>
+        <v>3.734642437678979</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -772,6 +778,14 @@
       </c>
       <c r="B13" s="1">
         <v>3.876469828143171</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B14" s="1">
+        <v>3.798017796426246</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/0500000US39049.xlsx
+++ b/output_data/charts/0500000US39049.xlsx
@@ -161,47 +161,32 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$14</c:f>
+              <c:f>Sheet1!$A$2:$A$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>2012</c:v>
+                  <c:v>2017</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2013</c:v>
+                  <c:v>2018</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2014</c:v>
+                  <c:v>2019</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2015</c:v>
+                  <c:v>2020</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2016</c:v>
+                  <c:v>2021</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2017</c:v>
+                  <c:v>2022</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2018</c:v>
+                  <c:v>2023</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2019</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>2020</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2021</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>2022</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>2023</c:v>
-                </c:pt>
-                <c:pt idx="12">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -209,47 +194,32 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$14</c:f>
+              <c:f>Sheet1!$B$2:$B$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>2.495390975623382</c:v>
+                  <c:v>2.744495326516529</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.588805266369571</c:v>
+                  <c:v>2.950727533878724</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.60772382962871</c:v>
+                  <c:v>3.005639293525972</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.624931262029145</c:v>
+                  <c:v>3.353293861950086</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.711712608219723</c:v>
+                  <c:v>3.549603975556453</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.744495326516529</c:v>
+                  <c:v>3.732333029811156</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.950727533878724</c:v>
+                  <c:v>3.876469828143171</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.005639293525972</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>3.357565764820505</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>3.549603975556453</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>3.734642437678979</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>3.876469828143171</c:v>
-                </c:pt>
-                <c:pt idx="12">
                   <c:v>3.798017796426246</c:v>
                 </c:pt>
               </c:numCache>
@@ -670,7 +640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" style="1" customWidth="1"/>
@@ -686,105 +656,65 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="B2" s="1">
-        <v>2.495390975623382</v>
+        <v>2.744495326516529</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="B3" s="1">
-        <v>2.588805266369571</v>
+        <v>2.950727533878724</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="B4" s="1">
-        <v>2.60772382962871</v>
+        <v>3.005639293525972</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="B5" s="1">
-        <v>2.624931262029145</v>
+        <v>3.353293861950086</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="B6" s="1">
-        <v>2.711712608219723</v>
+        <v>3.549603975556453</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="B7" s="1">
-        <v>2.744495326516529</v>
+        <v>3.732333029811156</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="B8" s="1">
-        <v>2.950727533878724</v>
+        <v>3.876469828143171</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="B9" s="1">
-        <v>3.005639293525972</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B10" s="1">
-        <v>3.357565764820505</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B11" s="1">
-        <v>3.549603975556453</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="2">
-        <v>2022</v>
-      </c>
-      <c r="B12" s="1">
-        <v>3.734642437678979</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="2">
-        <v>2023</v>
-      </c>
-      <c r="B13" s="1">
-        <v>3.876469828143171</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="2">
-        <v>2024</v>
-      </c>
-      <c r="B14" s="1">
         <v>3.798017796426246</v>
       </c>
     </row>

--- a/output_data/charts/0500000US39049.xlsx
+++ b/output_data/charts/0500000US39049.xlsx
@@ -161,32 +161,47 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$9</c:f>
+              <c:f>Sheet1!$A$2:$A$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>2017</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="6">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="7">
                   <c:v>2019</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="8">
                   <c:v>2020</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="9">
                   <c:v>2021</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="10">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="11">
                   <c:v>2023</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="12">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -194,32 +209,47 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$9</c:f>
+              <c:f>Sheet1!$B$2:$B$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
+                  <c:v>2.569880258477812</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.681262597311341</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.62546344751734</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.624931262029145</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.703419909112018</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>2.744495326516529</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="6">
                   <c:v>2.950727533878724</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="7">
                   <c:v>3.005639293525972</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="8">
                   <c:v>3.353293861950086</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="9">
                   <c:v>3.549603975556453</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="10">
                   <c:v>3.732333029811156</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="11">
                   <c:v>3.876469828143171</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="12">
                   <c:v>3.798017796426246</c:v>
                 </c:pt>
               </c:numCache>
@@ -640,7 +670,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" style="1" customWidth="1"/>
@@ -656,65 +686,105 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="B2" s="1">
-        <v>2.744495326516529</v>
+        <v>2.569880258477812</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="B3" s="1">
-        <v>2.950727533878724</v>
+        <v>2.681262597311341</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="B4" s="1">
-        <v>3.005639293525972</v>
+        <v>2.62546344751734</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="B5" s="1">
-        <v>3.353293861950086</v>
+        <v>2.624931262029145</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="B6" s="1">
-        <v>3.549603975556453</v>
+        <v>2.703419909112018</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="B7" s="1">
-        <v>3.732333029811156</v>
+        <v>2.744495326516529</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="B8" s="1">
-        <v>3.876469828143171</v>
+        <v>2.950727533878724</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
+        <v>2019</v>
+      </c>
+      <c r="B9" s="1">
+        <v>3.005639293525972</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B10" s="1">
+        <v>3.353293861950086</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B11" s="1">
+        <v>3.549603975556453</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B12" s="1">
+        <v>3.732333029811156</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B13" s="1">
+        <v>3.876469828143171</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2">
         <v>2024</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B14" s="1">
         <v>3.798017796426246</v>
       </c>
     </row>
